--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WISCONSIN_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/WISCONSIN_2013.xlsx
@@ -1608,7 +1608,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C70">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C203">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C520">
@@ -11166,7 +11166,7 @@
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C601">
@@ -11184,7 +11184,7 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C602">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="B630" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C630">
@@ -15990,7 +15990,7 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C869">
@@ -16332,7 +16332,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C888">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="B997" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C997">
